--- a/BWI/bestwine_output/bestwine_New Caledonia.xlsx
+++ b/BWI/bestwine_output/bestwine_New Caledonia.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,11 @@
     <font>
       <color rgb="00000000"/>
     </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +56,11 @@
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,13 +74,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1108,6 +1117,103 @@
       <c r="Z7" s="3" t="inlineStr"/>
       <c r="AA7" s="3" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Pavillon Des Vins</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Pavillon Des Vins</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>93307</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>New Caledonia</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Faubourg Blanchot</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Province Sud</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>97 Route De L'anse Vata</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>98800</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.nc</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>com.net.pavillon@gmail.com</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>+687 278020</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pavillon.desvins/</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>Pierre Gayraud</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pierre-gayraud-659a676b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_New Caledonia.xlsx
+++ b/BWI/bestwine_output/bestwine_New Caledonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1214,6 +1214,103 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Pavillon Des Vins</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Pavillon Des Vins</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>93307</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>New Caledonia</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Faubourg Blanchot</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Province Sud</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>97 Route De L'anse Vata</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>98800</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pavillondesvins.nc</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>com.net.pavillon@gmail.com</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>+687 278020</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pavillon.desvins/</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>Pierre Gayraud</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pierre-gayraud-659a676b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
